--- a/npc-reporting-system/sample_data/sample_data/AGUS1_Sample_Report.xlsx
+++ b/npc-reporting-system/sample_data/sample_data/AGUS1_Sample_Report.xlsx
@@ -485,56 +485,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>549753.5699999999</v>
+        <v>552027.23</v>
       </c>
       <c r="D2" t="n">
-        <v>19.65</v>
+        <v>22.35</v>
       </c>
       <c r="E2" t="n">
-        <v>20.24</v>
+        <v>22.36</v>
       </c>
       <c r="F2" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Forced outage due to equipment maintenance</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>404594.56</v>
+        <v>475224.81</v>
       </c>
       <c r="D3" t="n">
-        <v>16.34</v>
+        <v>18.5</v>
       </c>
       <c r="E3" t="n">
-        <v>20.33</v>
+        <v>20.51</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>2.71</v>
+        <v>0.62</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,20 +541,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>357430.76</v>
+        <v>365844.15</v>
       </c>
       <c r="D4" t="n">
-        <v>16.99</v>
+        <v>17.27</v>
       </c>
       <c r="E4" t="n">
-        <v>20.2</v>
+        <v>17.92</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -571,50 +567,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>448538.2</v>
+        <v>483964.64</v>
       </c>
       <c r="D5" t="n">
-        <v>19.58</v>
+        <v>17.04</v>
       </c>
       <c r="E5" t="n">
-        <v>21.7</v>
+        <v>17.04</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>6.96</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Forced outage due to equipment maintenance</t>
+          <t>Scheduled maintenance</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>369192.67</v>
+        <v>439146.13</v>
       </c>
       <c r="D6" t="n">
-        <v>17.39</v>
+        <v>20.47</v>
       </c>
       <c r="E6" t="n">
-        <v>19.9</v>
+        <v>21.84</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -627,20 +623,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>516439.41</v>
+        <v>454384.09</v>
       </c>
       <c r="D7" t="n">
-        <v>19.14</v>
+        <v>19.83</v>
       </c>
       <c r="E7" t="n">
-        <v>20.68</v>
+        <v>21.2</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -653,308 +649,296 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>383966.25</v>
+        <v>469265.19</v>
       </c>
       <c r="D8" t="n">
-        <v>16.08</v>
+        <v>17.52</v>
       </c>
       <c r="E8" t="n">
-        <v>18.52</v>
+        <v>21.22</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Forced outage due to equipment maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>432236.24</v>
+        <v>511238.91</v>
       </c>
       <c r="D9" t="n">
-        <v>18.5</v>
+        <v>19.66</v>
       </c>
       <c r="E9" t="n">
-        <v>18.5</v>
+        <v>21.78</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Scheduled maintenance</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>363945.84</v>
+        <v>379297.19</v>
       </c>
       <c r="D10" t="n">
-        <v>14.8</v>
+        <v>13.54</v>
       </c>
       <c r="E10" t="n">
-        <v>14.8</v>
+        <v>16.92</v>
       </c>
       <c r="F10" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>6.54</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Forced outage due to equipment maintenance</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>334720.81</v>
+        <v>485444.83</v>
       </c>
       <c r="D11" t="n">
-        <v>15.05</v>
+        <v>18.04</v>
       </c>
       <c r="E11" t="n">
-        <v>17.76</v>
+        <v>19.33</v>
       </c>
       <c r="F11" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Forced outage due to equipment maintenance</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>448203.34</v>
+        <v>411157.07</v>
       </c>
       <c r="D12" t="n">
-        <v>19.82</v>
+        <v>16.81</v>
       </c>
       <c r="E12" t="n">
-        <v>21.03</v>
+        <v>18.49</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
+        <v>3.33</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Scheduled maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>413047.01</v>
+        <v>435660.12</v>
       </c>
       <c r="D13" t="n">
-        <v>16.05</v>
+        <v>16.87</v>
       </c>
       <c r="E13" t="n">
-        <v>17.18</v>
+        <v>16.98</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Scheduled maintenance</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>453620.7</v>
+        <v>485268.23</v>
       </c>
       <c r="D14" t="n">
-        <v>19.8</v>
+        <v>17.97</v>
       </c>
       <c r="E14" t="n">
-        <v>20.43</v>
+        <v>19.5</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="G14" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Scheduled maintenance</t>
+          <t>Forced outage due to equipment maintenance</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>333526.51</v>
+        <v>362972.37</v>
       </c>
       <c r="D15" t="n">
-        <v>14.11</v>
+        <v>17.22</v>
       </c>
       <c r="E15" t="n">
-        <v>14.11</v>
+        <v>17.98</v>
       </c>
       <c r="F15" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Forced outage due to equipment maintenance</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>472749.14</v>
+        <v>512660.23</v>
       </c>
       <c r="D16" t="n">
-        <v>22.16</v>
+        <v>19.14</v>
       </c>
       <c r="E16" t="n">
-        <v>22.17</v>
+        <v>20.19</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
+        <v>1.75</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Forced outage due to equipment maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>445269.19</v>
+        <v>425285.58</v>
       </c>
       <c r="D17" t="n">
-        <v>20.02</v>
+        <v>17.34</v>
       </c>
       <c r="E17" t="n">
-        <v>20.7</v>
+        <v>19.72</v>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Forced outage due to equipment maintenance</t>
-        </is>
-      </c>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>442086.65</v>
+        <v>384243.11</v>
       </c>
       <c r="D18" t="n">
-        <v>17.84</v>
+        <v>17.64</v>
       </c>
       <c r="E18" t="n">
-        <v>21.27</v>
+        <v>18.78</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -967,46 +951,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>507157.69</v>
+        <v>490000.56</v>
       </c>
       <c r="D19" t="n">
-        <v>20.78</v>
+        <v>17.4</v>
       </c>
       <c r="E19" t="n">
-        <v>21.39</v>
+        <v>21.6</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Forced outage due to equipment maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>423220.87</v>
+        <v>515202.71</v>
       </c>
       <c r="D20" t="n">
-        <v>19</v>
+        <v>19.43</v>
       </c>
       <c r="E20" t="n">
-        <v>21.4</v>
+        <v>20.59</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1019,50 +1007,46 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>439587.59</v>
+        <v>411887.16</v>
       </c>
       <c r="D21" t="n">
-        <v>17.69</v>
+        <v>18.72</v>
       </c>
       <c r="E21" t="n">
-        <v>17.75</v>
+        <v>19.48</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>5.79</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Scheduled maintenance</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>531000.92</v>
+        <v>307576.59</v>
       </c>
       <c r="D22" t="n">
-        <v>19.09</v>
+        <v>14.48</v>
       </c>
       <c r="E22" t="n">
-        <v>19.74</v>
+        <v>17</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1075,50 +1059,46 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>456213.75</v>
+        <v>348756.06</v>
       </c>
       <c r="D23" t="n">
-        <v>16.75</v>
+        <v>14.68</v>
       </c>
       <c r="E23" t="n">
-        <v>20.15</v>
+        <v>17</v>
       </c>
       <c r="F23" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Forced outage due to equipment maintenance</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>340854.17</v>
+        <v>518059.75</v>
       </c>
       <c r="D24" t="n">
-        <v>15.98</v>
+        <v>18.78</v>
       </c>
       <c r="E24" t="n">
-        <v>17.4</v>
+        <v>18.89</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1131,23 +1111,23 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>387456.91</v>
+        <v>490438.66</v>
       </c>
       <c r="D25" t="n">
-        <v>17.66</v>
+        <v>18.68</v>
       </c>
       <c r="E25" t="n">
-        <v>20.55</v>
+        <v>19.57</v>
       </c>
       <c r="F25" t="n">
-        <v>1.13</v>
+        <v>2.57</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1161,20 +1141,20 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>460753.94</v>
+        <v>354163.79</v>
       </c>
       <c r="D26" t="n">
-        <v>17.58</v>
+        <v>16.72</v>
       </c>
       <c r="E26" t="n">
-        <v>18.02</v>
+        <v>18.05</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1187,20 +1167,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>478047.54</v>
+        <v>500807.63</v>
       </c>
       <c r="D27" t="n">
-        <v>18.2</v>
+        <v>17.94</v>
       </c>
       <c r="E27" t="n">
-        <v>21.42</v>
+        <v>20.07</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -1213,20 +1193,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>3</v>
       </c>
       <c r="C28" t="n">
-        <v>420306.08</v>
+        <v>382756.03</v>
       </c>
       <c r="D28" t="n">
-        <v>15.49</v>
+        <v>16.26</v>
       </c>
       <c r="E28" t="n">
-        <v>18.89</v>
+        <v>19.9</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -1239,76 +1219,80 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>419916.24</v>
+        <v>547333.39</v>
       </c>
       <c r="D29" t="n">
-        <v>16.88</v>
+        <v>19.92</v>
       </c>
       <c r="E29" t="n">
-        <v>20.19</v>
+        <v>20.44</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Forced outage due to equipment maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>418218.86</v>
+        <v>487091.58</v>
       </c>
       <c r="D30" t="n">
-        <v>17.43</v>
+        <v>17.19</v>
       </c>
       <c r="E30" t="n">
-        <v>18.28</v>
+        <v>17.94</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="G30" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Scheduled maintenance</t>
+          <t>Forced outage due to equipment maintenance</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>2</v>
       </c>
       <c r="C31" t="n">
-        <v>363740.46</v>
+        <v>450206.87</v>
       </c>
       <c r="D31" t="n">
-        <v>16.44</v>
+        <v>19.58</v>
       </c>
       <c r="E31" t="n">
-        <v>19.6</v>
+        <v>21.61</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1321,46 +1305,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>3</v>
       </c>
       <c r="C32" t="n">
-        <v>350960.14</v>
+        <v>460999.43</v>
       </c>
       <c r="D32" t="n">
-        <v>15.12</v>
+        <v>18.32</v>
       </c>
       <c r="E32" t="n">
-        <v>18.76</v>
+        <v>19.56</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Forced outage due to equipment maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>633167.79</v>
+        <v>456082.14</v>
       </c>
       <c r="D33" t="n">
-        <v>22.35</v>
+        <v>17.65</v>
       </c>
       <c r="E33" t="n">
-        <v>22.67</v>
+        <v>19.09</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -1373,20 +1361,20 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>487114.1</v>
+        <v>526441.4300000001</v>
       </c>
       <c r="D34" t="n">
-        <v>21.34</v>
+        <v>18.83</v>
       </c>
       <c r="E34" t="n">
-        <v>22.1</v>
+        <v>18.94</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -1399,222 +1387,218 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>2</v>
       </c>
       <c r="C35" t="n">
-        <v>493279.1</v>
+        <v>456070.71</v>
       </c>
       <c r="D35" t="n">
-        <v>18.72</v>
+        <v>19.85</v>
       </c>
       <c r="E35" t="n">
-        <v>19.68</v>
+        <v>19.85</v>
       </c>
       <c r="F35" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Forced outage due to equipment maintenance</t>
+          <t>Scheduled maintenance</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>387259.73</v>
+        <v>398330.66</v>
       </c>
       <c r="D36" t="n">
-        <v>17.41</v>
+        <v>16.74</v>
       </c>
       <c r="E36" t="n">
-        <v>19.3</v>
+        <v>16.76</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="G36" t="n">
-        <v>4.53</v>
+        <v>5.62</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Scheduled maintenance</t>
+          <t>Forced outage due to equipment maintenance</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>4</v>
       </c>
       <c r="C37" t="n">
-        <v>536468.9399999999</v>
+        <v>577207.7</v>
       </c>
       <c r="D37" t="n">
-        <v>19.77</v>
+        <v>21.56</v>
       </c>
       <c r="E37" t="n">
-        <v>20.92</v>
+        <v>22.7</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Scheduled maintenance</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>537345.91</v>
+        <v>505653.79</v>
       </c>
       <c r="D38" t="n">
-        <v>20.07</v>
+        <v>18.66</v>
       </c>
       <c r="E38" t="n">
-        <v>20.57</v>
+        <v>19.58</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="inlineStr"/>
+        <v>4.42</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Scheduled maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>363042.63</v>
+        <v>464980</v>
       </c>
       <c r="D39" t="n">
-        <v>16.8</v>
+        <v>20.39</v>
       </c>
       <c r="E39" t="n">
-        <v>17.14</v>
+        <v>20.96</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="inlineStr"/>
+        <v>3.04</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Scheduled maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>3</v>
       </c>
       <c r="C40" t="n">
-        <v>361232.13</v>
+        <v>422208.4</v>
       </c>
       <c r="D40" t="n">
-        <v>17.04</v>
+        <v>14.9</v>
       </c>
       <c r="E40" t="n">
-        <v>18.22</v>
+        <v>18.17</v>
       </c>
       <c r="F40" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Forced outage due to equipment maintenance</t>
-        </is>
-      </c>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>4</v>
       </c>
       <c r="C41" t="n">
-        <v>484091.81</v>
+        <v>456108.73</v>
       </c>
       <c r="D41" t="n">
-        <v>18.09</v>
+        <v>16.4</v>
       </c>
       <c r="E41" t="n">
-        <v>20.51</v>
+        <v>19.47</v>
       </c>
       <c r="F41" t="n">
-        <v>0.57</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Forced outage due to equipment maintenance</t>
-        </is>
-      </c>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>426777.43</v>
+        <v>463212.02</v>
       </c>
       <c r="D42" t="n">
-        <v>16.23</v>
+        <v>18.21</v>
       </c>
       <c r="E42" t="n">
-        <v>18.26</v>
+        <v>21.92</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -1627,46 +1611,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>2</v>
       </c>
       <c r="C43" t="n">
-        <v>395432.26</v>
+        <v>441353</v>
       </c>
       <c r="D43" t="n">
-        <v>15.43</v>
+        <v>17.98</v>
       </c>
       <c r="E43" t="n">
-        <v>17.18</v>
+        <v>19.86</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
-      <c r="H43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Forced outage due to equipment maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>3</v>
       </c>
       <c r="C44" t="n">
-        <v>447774.07</v>
+        <v>466049.51</v>
       </c>
       <c r="D44" t="n">
-        <v>19.33</v>
+        <v>19.09</v>
       </c>
       <c r="E44" t="n">
-        <v>19.91</v>
+        <v>19.51</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -1679,23 +1667,23 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>4</v>
       </c>
       <c r="C45" t="n">
-        <v>449190.39</v>
+        <v>386868.03</v>
       </c>
       <c r="D45" t="n">
-        <v>17.45</v>
+        <v>13.64</v>
       </c>
       <c r="E45" t="n">
-        <v>18.17</v>
+        <v>17</v>
       </c>
       <c r="F45" t="n">
-        <v>1.38</v>
+        <v>2.91</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1709,26 +1697,26 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>485793.45</v>
+        <v>362503.05</v>
       </c>
       <c r="D46" t="n">
-        <v>18.85</v>
+        <v>16.24</v>
       </c>
       <c r="E46" t="n">
-        <v>19.08</v>
+        <v>18.03</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>2.43</v>
+        <v>0.39</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -1739,26 +1727,26 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>2</v>
       </c>
       <c r="C47" t="n">
-        <v>356206.46</v>
+        <v>420307.75</v>
       </c>
       <c r="D47" t="n">
-        <v>14.93</v>
+        <v>15.23</v>
       </c>
       <c r="E47" t="n">
-        <v>17.73</v>
+        <v>16.92</v>
       </c>
       <c r="F47" t="n">
-        <v>1.78</v>
+        <v>2.88</v>
       </c>
       <c r="G47" t="n">
-        <v>0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -1769,26 +1757,26 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>3</v>
       </c>
       <c r="C48" t="n">
-        <v>501306.38</v>
+        <v>406164.27</v>
       </c>
       <c r="D48" t="n">
-        <v>19.05</v>
+        <v>14.88</v>
       </c>
       <c r="E48" t="n">
-        <v>21.03</v>
+        <v>18.07</v>
       </c>
       <c r="F48" t="n">
-        <v>0.93</v>
+        <v>0.03</v>
       </c>
       <c r="G48" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -1799,20 +1787,20 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>4</v>
       </c>
       <c r="C49" t="n">
-        <v>383025.81</v>
+        <v>397364.77</v>
       </c>
       <c r="D49" t="n">
-        <v>16.92</v>
+        <v>18.25</v>
       </c>
       <c r="E49" t="n">
-        <v>20.03</v>
+        <v>19.42</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -1825,26 +1813,26 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>381852.81</v>
+        <v>484187.99</v>
       </c>
       <c r="D50" t="n">
-        <v>15.81</v>
+        <v>20.16</v>
       </c>
       <c r="E50" t="n">
-        <v>17.89</v>
+        <v>21.78</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>2.95</v>
+        <v>1.76</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -1855,162 +1843,158 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>2</v>
       </c>
       <c r="C51" t="n">
-        <v>491606.56</v>
+        <v>382801.96</v>
       </c>
       <c r="D51" t="n">
-        <v>17.51</v>
+        <v>17.07</v>
       </c>
       <c r="E51" t="n">
-        <v>17.94</v>
+        <v>19.58</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="inlineStr"/>
+        <v>3.38</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Scheduled maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>3</v>
       </c>
       <c r="C52" t="n">
-        <v>418410.96</v>
+        <v>571442.8100000001</v>
       </c>
       <c r="D52" t="n">
-        <v>15.1</v>
+        <v>21.27</v>
       </c>
       <c r="E52" t="n">
-        <v>15.1</v>
+        <v>22.55</v>
       </c>
       <c r="F52" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>7.83</v>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Forced outage due to equipment maintenance</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>4</v>
       </c>
       <c r="C53" t="n">
-        <v>447388.81</v>
+        <v>444794.8</v>
       </c>
       <c r="D53" t="n">
-        <v>18.26</v>
+        <v>18.78</v>
       </c>
       <c r="E53" t="n">
-        <v>21.6</v>
+        <v>18.78</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="inlineStr"/>
+        <v>5.22</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Scheduled maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>354974.87</v>
+        <v>372042.86</v>
       </c>
       <c r="D54" t="n">
-        <v>15.92</v>
+        <v>14.11</v>
       </c>
       <c r="E54" t="n">
-        <v>17.97</v>
+        <v>16.92</v>
       </c>
       <c r="F54" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Forced outage due to equipment maintenance</t>
-        </is>
-      </c>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>2</v>
       </c>
       <c r="C55" t="n">
-        <v>456342.14</v>
+        <v>369016.9</v>
       </c>
       <c r="D55" t="n">
-        <v>16.11</v>
+        <v>17.02</v>
       </c>
       <c r="E55" t="n">
-        <v>16.5</v>
+        <v>20.74</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Scheduled maintenance</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>3</v>
       </c>
       <c r="C56" t="n">
-        <v>423844.37</v>
+        <v>460718.16</v>
       </c>
       <c r="D56" t="n">
-        <v>19.16</v>
+        <v>18.64</v>
       </c>
       <c r="E56" t="n">
-        <v>20.55</v>
+        <v>21.61</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -2023,23 +2007,23 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>4</v>
       </c>
       <c r="C57" t="n">
-        <v>487348.05</v>
+        <v>428674.27</v>
       </c>
       <c r="D57" t="n">
-        <v>18.06</v>
+        <v>16.86</v>
       </c>
       <c r="E57" t="n">
-        <v>21.92</v>
+        <v>18.65</v>
       </c>
       <c r="F57" t="n">
-        <v>1.78</v>
+        <v>0.66</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -2053,106 +2037,102 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>1</v>
       </c>
       <c r="C58" t="n">
-        <v>500391.71</v>
+        <v>534632.92</v>
       </c>
       <c r="D58" t="n">
-        <v>17.6</v>
+        <v>19.61</v>
       </c>
       <c r="E58" t="n">
-        <v>17.6</v>
+        <v>20.35</v>
       </c>
       <c r="F58" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Forced outage due to equipment maintenance</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>2</v>
       </c>
       <c r="C59" t="n">
-        <v>407534.7</v>
+        <v>510531.78</v>
       </c>
       <c r="D59" t="n">
-        <v>16.22</v>
+        <v>18.35</v>
       </c>
       <c r="E59" t="n">
-        <v>17.54</v>
+        <v>18.43</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" t="inlineStr"/>
+        <v>1.61</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Scheduled maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B60" t="n">
         <v>3</v>
       </c>
       <c r="C60" t="n">
-        <v>462508.26</v>
+        <v>368156.16</v>
       </c>
       <c r="D60" t="n">
-        <v>18.91</v>
+        <v>17.08</v>
       </c>
       <c r="E60" t="n">
-        <v>20.26</v>
+        <v>17.61</v>
       </c>
       <c r="F60" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Forced outage due to equipment maintenance</t>
-        </is>
-      </c>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>4</v>
       </c>
       <c r="C61" t="n">
-        <v>406305.81</v>
+        <v>556823.8100000001</v>
       </c>
       <c r="D61" t="n">
-        <v>15.89</v>
+        <v>22.21</v>
       </c>
       <c r="E61" t="n">
-        <v>19.69</v>
+        <v>22.65</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -2165,154 +2145,166 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>1</v>
       </c>
       <c r="C62" t="n">
-        <v>420542.58</v>
+        <v>355465.25</v>
       </c>
       <c r="D62" t="n">
-        <v>17.94</v>
+        <v>15.43</v>
       </c>
       <c r="E62" t="n">
-        <v>19.15</v>
+        <v>18.79</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="inlineStr"/>
+        <v>2.35</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Forced outage due to equipment maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>2</v>
       </c>
       <c r="C63" t="n">
-        <v>332875.3</v>
+        <v>487162.37</v>
       </c>
       <c r="D63" t="n">
-        <v>14.01</v>
+        <v>19.65</v>
       </c>
       <c r="E63" t="n">
-        <v>17.26</v>
+        <v>20.63</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="inlineStr"/>
+        <v>2.67</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Scheduled maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>3</v>
       </c>
       <c r="C64" t="n">
-        <v>427583.14</v>
+        <v>528170.1800000001</v>
       </c>
       <c r="D64" t="n">
-        <v>16.05</v>
+        <v>21.79</v>
       </c>
       <c r="E64" t="n">
-        <v>19.53</v>
+        <v>22.14</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Scheduled maintenance</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>4</v>
       </c>
       <c r="C65" t="n">
-        <v>372432.92</v>
+        <v>374051.79</v>
       </c>
       <c r="D65" t="n">
-        <v>17.21</v>
+        <v>15.61</v>
       </c>
       <c r="E65" t="n">
-        <v>18.26</v>
+        <v>15.61</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" t="inlineStr"/>
+        <v>7.09</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Forced outage due to equipment maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>1</v>
       </c>
       <c r="C66" t="n">
-        <v>328132.31</v>
+        <v>326308.76</v>
       </c>
       <c r="D66" t="n">
-        <v>14.91</v>
+        <v>14.89</v>
       </c>
       <c r="E66" t="n">
-        <v>18.03</v>
+        <v>18.31</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
-      <c r="H66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Forced outage due to equipment maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>2</v>
       </c>
       <c r="C67" t="n">
-        <v>589978.75</v>
+        <v>419350.25</v>
       </c>
       <c r="D67" t="n">
-        <v>21.41</v>
+        <v>15.21</v>
       </c>
       <c r="E67" t="n">
-        <v>21.94</v>
+        <v>18.85</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -2325,20 +2317,20 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>3</v>
       </c>
       <c r="C68" t="n">
-        <v>459907.68</v>
+        <v>395444.21</v>
       </c>
       <c r="D68" t="n">
-        <v>17.2</v>
+        <v>16.64</v>
       </c>
       <c r="E68" t="n">
-        <v>18.02</v>
+        <v>18.9</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -2351,20 +2343,20 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>4</v>
       </c>
       <c r="C69" t="n">
-        <v>433535.74</v>
+        <v>463760.19</v>
       </c>
       <c r="D69" t="n">
-        <v>17.14</v>
+        <v>18.8</v>
       </c>
       <c r="E69" t="n">
-        <v>21.3</v>
+        <v>20.41</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -2377,158 +2369,162 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>402111.69</v>
+        <v>426713.76</v>
       </c>
       <c r="D70" t="n">
-        <v>16.09</v>
+        <v>19.54</v>
       </c>
       <c r="E70" t="n">
-        <v>17.07</v>
+        <v>19.54</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="inlineStr"/>
+        <v>4.46</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Scheduled maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>2</v>
       </c>
       <c r="C71" t="n">
-        <v>412336.02</v>
+        <v>472306.39</v>
       </c>
       <c r="D71" t="n">
-        <v>16.22</v>
+        <v>17.48</v>
       </c>
       <c r="E71" t="n">
-        <v>18.16</v>
+        <v>17.48</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" t="inlineStr"/>
+        <v>4.98</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Forced outage due to equipment maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B72" t="n">
         <v>3</v>
       </c>
       <c r="C72" t="n">
-        <v>514202</v>
+        <v>394604.56</v>
       </c>
       <c r="D72" t="n">
-        <v>19</v>
+        <v>14.73</v>
       </c>
       <c r="E72" t="n">
-        <v>22.56</v>
+        <v>18.25</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
-      <c r="H72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Forced outage due to equipment maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>4</v>
       </c>
       <c r="C73" t="n">
-        <v>428322.52</v>
+        <v>509833.7</v>
       </c>
       <c r="D73" t="n">
-        <v>18.76</v>
+        <v>21.57</v>
       </c>
       <c r="E73" t="n">
-        <v>19.2</v>
+        <v>22.52</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Scheduled maintenance</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>472836.85</v>
+        <v>550242.25</v>
       </c>
       <c r="D74" t="n">
-        <v>19.16</v>
+        <v>19.57</v>
       </c>
       <c r="E74" t="n">
-        <v>20.84</v>
+        <v>19.93</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Scheduled maintenance</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>2</v>
       </c>
       <c r="C75" t="n">
-        <v>390671.64</v>
+        <v>375589.8</v>
       </c>
       <c r="D75" t="n">
-        <v>15.9</v>
+        <v>17.66</v>
       </c>
       <c r="E75" t="n">
-        <v>17.72</v>
+        <v>22.03</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
@@ -2541,112 +2537,112 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>3</v>
       </c>
       <c r="C76" t="n">
-        <v>341194.33</v>
+        <v>487288.83</v>
       </c>
       <c r="D76" t="n">
-        <v>15.38</v>
+        <v>20.74</v>
       </c>
       <c r="E76" t="n">
-        <v>15.38</v>
+        <v>21.16</v>
       </c>
       <c r="F76" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>6.58</v>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Forced outage due to equipment maintenance</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>4</v>
       </c>
       <c r="C77" t="n">
-        <v>444860.72</v>
+        <v>421360.61</v>
       </c>
       <c r="D77" t="n">
-        <v>18.59</v>
+        <v>16.34</v>
       </c>
       <c r="E77" t="n">
-        <v>20.45</v>
+        <v>16.34</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="G77" t="n">
-        <v>0.35</v>
+        <v>6.43</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Scheduled maintenance</t>
+          <t>Forced outage due to equipment maintenance</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B78" t="n">
         <v>1</v>
       </c>
       <c r="C78" t="n">
-        <v>546251.16</v>
+        <v>421936.17</v>
       </c>
       <c r="D78" t="n">
-        <v>19.56</v>
+        <v>14.95</v>
       </c>
       <c r="E78" t="n">
-        <v>21.37</v>
+        <v>17.44</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
-      <c r="H78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Forced outage due to equipment maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>2</v>
       </c>
       <c r="C79" t="n">
-        <v>365039.41</v>
+        <v>560366.36</v>
       </c>
       <c r="D79" t="n">
-        <v>16.82</v>
+        <v>21.42</v>
       </c>
       <c r="E79" t="n">
-        <v>18.28</v>
+        <v>21.42</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>5.72</v>
+        <v>2.58</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -2657,20 +2653,20 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>3</v>
       </c>
       <c r="C80" t="n">
-        <v>603639.03</v>
+        <v>388310.89</v>
       </c>
       <c r="D80" t="n">
-        <v>21.82</v>
+        <v>14.44</v>
       </c>
       <c r="E80" t="n">
-        <v>22.17</v>
+        <v>17.28</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
@@ -2683,20 +2679,20 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B81" t="n">
         <v>4</v>
       </c>
       <c r="C81" t="n">
-        <v>413598.12</v>
+        <v>369182.47</v>
       </c>
       <c r="D81" t="n">
-        <v>16.01</v>
+        <v>16.07</v>
       </c>
       <c r="E81" t="n">
-        <v>17.26</v>
+        <v>19.53</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -2709,20 +2705,20 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>1</v>
       </c>
       <c r="C82" t="n">
-        <v>407783.31</v>
+        <v>498354.94</v>
       </c>
       <c r="D82" t="n">
-        <v>16.01</v>
+        <v>18.45</v>
       </c>
       <c r="E82" t="n">
-        <v>19.59</v>
+        <v>19.58</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -2735,26 +2731,26 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>2</v>
       </c>
       <c r="C83" t="n">
-        <v>462270.2</v>
+        <v>324386.16</v>
       </c>
       <c r="D83" t="n">
-        <v>16.96</v>
+        <v>15.24</v>
       </c>
       <c r="E83" t="n">
-        <v>21</v>
+        <v>15.24</v>
       </c>
       <c r="F83" t="n">
-        <v>0.51</v>
+        <v>2.99</v>
       </c>
       <c r="G83" t="n">
-        <v>0.79</v>
+        <v>5.77</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -2765,20 +2761,20 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>3</v>
       </c>
       <c r="C84" t="n">
-        <v>428131.08</v>
+        <v>343913.34</v>
       </c>
       <c r="D84" t="n">
-        <v>15.84</v>
+        <v>14.08</v>
       </c>
       <c r="E84" t="n">
-        <v>17.22</v>
+        <v>16.88</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
@@ -2791,110 +2787,106 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>4</v>
       </c>
       <c r="C85" t="n">
-        <v>538435.16</v>
+        <v>389677.92</v>
       </c>
       <c r="D85" t="n">
-        <v>19.31</v>
+        <v>17.34</v>
       </c>
       <c r="E85" t="n">
-        <v>22.18</v>
+        <v>20.31</v>
       </c>
       <c r="F85" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Forced outage due to equipment maintenance</t>
-        </is>
-      </c>
+      <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>1</v>
       </c>
       <c r="C86" t="n">
-        <v>410612.82</v>
+        <v>351871.1</v>
       </c>
       <c r="D86" t="n">
-        <v>18.84</v>
+        <v>15.98</v>
       </c>
       <c r="E86" t="n">
-        <v>22.11</v>
+        <v>19.38</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="G86" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Scheduled maintenance</t>
+          <t>Forced outage due to equipment maintenance</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>2</v>
       </c>
       <c r="C87" t="n">
-        <v>366007.88</v>
+        <v>373350.66</v>
       </c>
       <c r="D87" t="n">
-        <v>16.92</v>
+        <v>13.76</v>
       </c>
       <c r="E87" t="n">
-        <v>17.77</v>
+        <v>13.76</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="G87" t="n">
-        <v>6.23</v>
+        <v>7.7</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Scheduled maintenance</t>
+          <t>Forced outage due to equipment maintenance</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>3</v>
       </c>
       <c r="C88" t="n">
-        <v>497223.18</v>
+        <v>430241.51</v>
       </c>
       <c r="D88" t="n">
-        <v>21.16</v>
+        <v>17.38</v>
       </c>
       <c r="E88" t="n">
-        <v>21.37</v>
+        <v>18.94</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -2907,20 +2899,20 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>4</v>
       </c>
       <c r="C89" t="n">
-        <v>414018.49</v>
+        <v>536589.78</v>
       </c>
       <c r="D89" t="n">
-        <v>16.54</v>
+        <v>20.67</v>
       </c>
       <c r="E89" t="n">
-        <v>18.42</v>
+        <v>21.63</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -2933,20 +2925,20 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>1</v>
       </c>
       <c r="C90" t="n">
-        <v>377103.71</v>
+        <v>416955.37</v>
       </c>
       <c r="D90" t="n">
-        <v>14.24</v>
+        <v>14.91</v>
       </c>
       <c r="E90" t="n">
-        <v>17.27</v>
+        <v>17.98</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -2959,82 +2951,82 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>2</v>
       </c>
       <c r="C91" t="n">
-        <v>369177.02</v>
+        <v>542080.5600000001</v>
       </c>
       <c r="D91" t="n">
-        <v>13.96</v>
+        <v>19.21</v>
       </c>
       <c r="E91" t="n">
-        <v>17.37</v>
+        <v>21.66</v>
       </c>
       <c r="F91" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Forced outage due to equipment maintenance</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B92" t="n">
         <v>3</v>
       </c>
       <c r="C92" t="n">
-        <v>427533.92</v>
+        <v>438510.77</v>
       </c>
       <c r="D92" t="n">
-        <v>15.98</v>
+        <v>16.75</v>
       </c>
       <c r="E92" t="n">
-        <v>17.85</v>
+        <v>18.14</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
       </c>
-      <c r="H92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Forced outage due to equipment maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B93" t="n">
         <v>4</v>
       </c>
       <c r="C93" t="n">
-        <v>355032.34</v>
+        <v>431119.53</v>
       </c>
       <c r="D93" t="n">
-        <v>13.89</v>
+        <v>19.52</v>
       </c>
       <c r="E93" t="n">
-        <v>17.31</v>
+        <v>19.52</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>3.39</v>
+        <v>4.48</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -3045,106 +3037,106 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B94" t="n">
         <v>1</v>
       </c>
       <c r="C94" t="n">
-        <v>378418.09</v>
+        <v>394297.71</v>
       </c>
       <c r="D94" t="n">
-        <v>14.23</v>
+        <v>18.6</v>
       </c>
       <c r="E94" t="n">
-        <v>16.93</v>
+        <v>21.8</v>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="G94" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Scheduled maintenance</t>
+          <t>Forced outage due to equipment maintenance</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B95" t="n">
         <v>2</v>
       </c>
       <c r="C95" t="n">
-        <v>564572.84</v>
+        <v>459991.94</v>
       </c>
       <c r="D95" t="n">
-        <v>20.65</v>
+        <v>16.67</v>
       </c>
       <c r="E95" t="n">
-        <v>21.48</v>
+        <v>18.07</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
       </c>
-      <c r="H95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Forced outage due to equipment maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B96" t="n">
         <v>3</v>
       </c>
       <c r="C96" t="n">
-        <v>455763.44</v>
+        <v>393954.48</v>
       </c>
       <c r="D96" t="n">
-        <v>16.01</v>
+        <v>17.85</v>
       </c>
       <c r="E96" t="n">
-        <v>17.55</v>
+        <v>19.49</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>6.22</v>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Scheduled maintenance</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B97" t="n">
         <v>4</v>
       </c>
       <c r="C97" t="n">
-        <v>525454.14</v>
+        <v>408184.28</v>
       </c>
       <c r="D97" t="n">
-        <v>20.51</v>
+        <v>19.12</v>
       </c>
       <c r="E97" t="n">
-        <v>21.83</v>
+        <v>20.66</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
@@ -3157,56 +3149,52 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B98" t="n">
         <v>1</v>
       </c>
       <c r="C98" t="n">
-        <v>359059.85</v>
+        <v>376034.76</v>
       </c>
       <c r="D98" t="n">
-        <v>16.03</v>
+        <v>17.41</v>
       </c>
       <c r="E98" t="n">
-        <v>19.92</v>
+        <v>17.63</v>
       </c>
       <c r="F98" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Forced outage due to equipment maintenance</t>
-        </is>
-      </c>
+      <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B99" t="n">
         <v>2</v>
       </c>
       <c r="C99" t="n">
-        <v>413184.33</v>
+        <v>356990.91</v>
       </c>
       <c r="D99" t="n">
-        <v>15.66</v>
+        <v>15.92</v>
       </c>
       <c r="E99" t="n">
-        <v>19.48</v>
+        <v>19.55</v>
       </c>
       <c r="F99" t="n">
-        <v>2.67</v>
+        <v>2.13</v>
       </c>
       <c r="G99" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -3217,134 +3205,146 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B100" t="n">
         <v>3</v>
       </c>
       <c r="C100" t="n">
-        <v>412443.99</v>
+        <v>408252.15</v>
       </c>
       <c r="D100" t="n">
-        <v>15.55</v>
+        <v>17.29</v>
       </c>
       <c r="E100" t="n">
-        <v>16.17</v>
+        <v>18.06</v>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="G100" t="n">
-        <v>7.83</v>
+        <v>0</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Scheduled maintenance</t>
+          <t>Forced outage due to equipment maintenance</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B101" t="n">
         <v>4</v>
       </c>
       <c r="C101" t="n">
-        <v>406277.07</v>
+        <v>414160.76</v>
       </c>
       <c r="D101" t="n">
-        <v>16.12</v>
+        <v>17.42</v>
       </c>
       <c r="E101" t="n">
-        <v>18.39</v>
+        <v>18.21</v>
       </c>
       <c r="F101" t="n">
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" t="inlineStr"/>
+        <v>5.79</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Scheduled maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B102" t="n">
         <v>1</v>
       </c>
       <c r="C102" t="n">
-        <v>402354.97</v>
+        <v>358855.6</v>
       </c>
       <c r="D102" t="n">
-        <v>16.21</v>
+        <v>15.71</v>
       </c>
       <c r="E102" t="n">
-        <v>16.83</v>
+        <v>18.88</v>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
       </c>
-      <c r="H102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Forced outage due to equipment maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B103" t="n">
         <v>2</v>
       </c>
       <c r="C103" t="n">
-        <v>352859.77</v>
+        <v>335864.4</v>
       </c>
       <c r="D103" t="n">
-        <v>15.7</v>
+        <v>15.59</v>
       </c>
       <c r="E103" t="n">
-        <v>18.51</v>
+        <v>17.87</v>
       </c>
       <c r="F103" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
       </c>
-      <c r="H103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Forced outage due to equipment maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B104" t="n">
         <v>3</v>
       </c>
       <c r="C104" t="n">
-        <v>383599.29</v>
+        <v>358498.61</v>
       </c>
       <c r="D104" t="n">
-        <v>16.87</v>
+        <v>16.53</v>
       </c>
       <c r="E104" t="n">
-        <v>18.37</v>
+        <v>19.97</v>
       </c>
       <c r="F104" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="G104" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -3355,76 +3355,76 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B105" t="n">
         <v>4</v>
       </c>
       <c r="C105" t="n">
-        <v>385786.93</v>
+        <v>367235.23</v>
       </c>
       <c r="D105" t="n">
         <v>16.24</v>
       </c>
       <c r="E105" t="n">
-        <v>17.74</v>
+        <v>17.28</v>
       </c>
       <c r="F105" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Forced outage due to equipment maintenance</t>
-        </is>
-      </c>
+      <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B106" t="n">
         <v>1</v>
       </c>
       <c r="C106" t="n">
-        <v>468891.58</v>
+        <v>439683.84</v>
       </c>
       <c r="D106" t="n">
-        <v>19.36</v>
+        <v>16.82</v>
       </c>
       <c r="E106" t="n">
-        <v>20.03</v>
+        <v>17.08</v>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
       </c>
-      <c r="H106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Forced outage due to equipment maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B107" t="n">
         <v>2</v>
       </c>
       <c r="C107" t="n">
-        <v>468410.33</v>
+        <v>334269.04</v>
       </c>
       <c r="D107" t="n">
-        <v>18.21</v>
+        <v>14.78</v>
       </c>
       <c r="E107" t="n">
-        <v>19.03</v>
+        <v>18.46</v>
       </c>
       <c r="F107" t="n">
         <v>0</v>
@@ -3437,170 +3437,158 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B108" t="n">
         <v>3</v>
       </c>
       <c r="C108" t="n">
-        <v>430507.39</v>
+        <v>517034.79</v>
       </c>
       <c r="D108" t="n">
-        <v>17.39</v>
+        <v>18.78</v>
       </c>
       <c r="E108" t="n">
-        <v>18</v>
+        <v>18.83</v>
       </c>
       <c r="F108" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="G108" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Scheduled maintenance</t>
+          <t>Forced outage due to equipment maintenance</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B109" t="n">
         <v>4</v>
       </c>
       <c r="C109" t="n">
-        <v>416703.58</v>
+        <v>466381.49</v>
       </c>
       <c r="D109" t="n">
-        <v>17.27</v>
+        <v>17.37</v>
       </c>
       <c r="E109" t="n">
-        <v>20.28</v>
+        <v>17.56</v>
       </c>
       <c r="F109" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Forced outage due to equipment maintenance</t>
-        </is>
-      </c>
+      <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B110" t="n">
         <v>1</v>
       </c>
       <c r="C110" t="n">
-        <v>448223.4</v>
+        <v>426420.03</v>
       </c>
       <c r="D110" t="n">
-        <v>17.41</v>
+        <v>19.09</v>
       </c>
       <c r="E110" t="n">
-        <v>17.41</v>
+        <v>21.49</v>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="G110" t="n">
-        <v>6.59</v>
+        <v>0</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Scheduled maintenance</t>
+          <t>Forced outage due to equipment maintenance</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B111" t="n">
         <v>2</v>
       </c>
       <c r="C111" t="n">
-        <v>409514.11</v>
+        <v>366556.67</v>
       </c>
       <c r="D111" t="n">
-        <v>17.97</v>
+        <v>15.97</v>
       </c>
       <c r="E111" t="n">
-        <v>21.78</v>
+        <v>19.04</v>
       </c>
       <c r="F111" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Forced outage due to equipment maintenance</t>
-        </is>
-      </c>
+      <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B112" t="n">
         <v>3</v>
       </c>
       <c r="C112" t="n">
-        <v>438395.57</v>
+        <v>432574.04</v>
       </c>
       <c r="D112" t="n">
-        <v>16.65</v>
+        <v>17.99</v>
       </c>
       <c r="E112" t="n">
-        <v>17.23</v>
+        <v>21.89</v>
       </c>
       <c r="F112" t="n">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Forced outage due to equipment maintenance</t>
-        </is>
-      </c>
+      <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B113" t="n">
         <v>4</v>
       </c>
       <c r="C113" t="n">
-        <v>430302.69</v>
+        <v>418796.49</v>
       </c>
       <c r="D113" t="n">
-        <v>17.42</v>
+        <v>16.82</v>
       </c>
       <c r="E113" t="n">
-        <v>19.24</v>
+        <v>19.62</v>
       </c>
       <c r="F113" t="n">
         <v>0</v>
@@ -3613,80 +3601,76 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B114" t="n">
         <v>1</v>
       </c>
       <c r="C114" t="n">
-        <v>327311.17</v>
+        <v>594831.51</v>
       </c>
       <c r="D114" t="n">
-        <v>15.52</v>
+        <v>21.88</v>
       </c>
       <c r="E114" t="n">
-        <v>17.94</v>
+        <v>22.6</v>
       </c>
       <c r="F114" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Forced outage due to equipment maintenance</t>
-        </is>
-      </c>
+      <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B115" t="n">
         <v>2</v>
       </c>
       <c r="C115" t="n">
-        <v>537954.87</v>
+        <v>446039.49</v>
       </c>
       <c r="D115" t="n">
-        <v>19.4</v>
+        <v>15.99</v>
       </c>
       <c r="E115" t="n">
-        <v>21.08</v>
+        <v>18.04</v>
       </c>
       <c r="F115" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>5.96</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Forced outage due to equipment maintenance</t>
+          <t>Scheduled maintenance</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B116" t="n">
         <v>3</v>
       </c>
       <c r="C116" t="n">
-        <v>372445.78</v>
+        <v>484139.15</v>
       </c>
       <c r="D116" t="n">
-        <v>14.27</v>
+        <v>21.4</v>
       </c>
       <c r="E116" t="n">
-        <v>16.98</v>
+        <v>22.19</v>
       </c>
       <c r="F116" t="n">
         <v>0</v>
@@ -3699,20 +3683,20 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B117" t="n">
         <v>4</v>
       </c>
       <c r="C117" t="n">
-        <v>485752.04</v>
+        <v>356195.96</v>
       </c>
       <c r="D117" t="n">
-        <v>19.05</v>
+        <v>15.42</v>
       </c>
       <c r="E117" t="n">
-        <v>20.62</v>
+        <v>17.38</v>
       </c>
       <c r="F117" t="n">
         <v>0</v>
@@ -3725,20 +3709,20 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B118" t="n">
         <v>1</v>
       </c>
       <c r="C118" t="n">
-        <v>495464.83</v>
+        <v>434729.64</v>
       </c>
       <c r="D118" t="n">
-        <v>19.64</v>
+        <v>19.15</v>
       </c>
       <c r="E118" t="n">
-        <v>21.29</v>
+        <v>21.73</v>
       </c>
       <c r="F118" t="n">
         <v>0</v>
@@ -3751,72 +3735,80 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B119" t="n">
         <v>2</v>
       </c>
       <c r="C119" t="n">
-        <v>459427.97</v>
+        <v>363345.61</v>
       </c>
       <c r="D119" t="n">
-        <v>19.96</v>
+        <v>14.64</v>
       </c>
       <c r="E119" t="n">
-        <v>21.89</v>
+        <v>17.1</v>
       </c>
       <c r="F119" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
       </c>
-      <c r="H119" t="inlineStr"/>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Forced outage due to equipment maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B120" t="n">
         <v>3</v>
       </c>
       <c r="C120" t="n">
-        <v>420127.11</v>
+        <v>414176.16</v>
       </c>
       <c r="D120" t="n">
-        <v>16.63</v>
+        <v>17.08</v>
       </c>
       <c r="E120" t="n">
-        <v>16.89</v>
+        <v>17.08</v>
       </c>
       <c r="F120" t="n">
         <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
-      </c>
-      <c r="H120" t="inlineStr"/>
+        <v>6.92</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Scheduled maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B121" t="n">
         <v>4</v>
       </c>
       <c r="C121" t="n">
-        <v>417481.43</v>
+        <v>417163.54</v>
       </c>
       <c r="D121" t="n">
-        <v>15.96</v>
+        <v>18.44</v>
       </c>
       <c r="E121" t="n">
-        <v>17.78</v>
+        <v>19.07</v>
       </c>
       <c r="F121" t="n">
         <v>0</v>
